--- a/examples/extensions/thai_bim/examples/stairs-two-point-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stairs-two-point-BBS.xlsx
@@ -179,7 +179,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -603,7 +603,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBIM Stair ST-02 e97999d4</t>
+          <t xml:space="preserve">TBIM Stair ST-02 0ccd08cd</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1328,12 +1328,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a0dc7fcaf2c64651</t>
+          <t xml:space="preserve">32e3ad58a377419a</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -1401,12 +1401,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c216db0fa0b44cef</t>
+          <t xml:space="preserve">cf9fe5cc105b4705</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">681b22d127e24758</t>
+          <t xml:space="preserve">92bb8b28154e4525</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">79c645dd771848ff</t>
+          <t xml:space="preserve">60c4cd79d78e4f41</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">809849790b134cba</t>
+          <t xml:space="preserve">966fbf29493545c6</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f425afa6b21c40ab</t>
+          <t xml:space="preserve">52cdf348f88048cc</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1766,12 +1766,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">294bb93f814d47f4</t>
+          <t xml:space="preserve">d7897c7d499d43b1</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">37e8573b0ebd4609</t>
+          <t xml:space="preserve">2f99b39e22594bcb</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cae896a7a5d14e16</t>
+          <t xml:space="preserve">d9d9429d0002417f</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fd075ab722384a6b</t>
+          <t xml:space="preserve">cdc442553abd4134</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2058,12 +2058,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">957917651b484d2c</t>
+          <t xml:space="preserve">76b50eeee97745da</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6d2ed981057d41c3</t>
+          <t xml:space="preserve">680e2858a7cd43e6</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">52def9c1724542c5</t>
+          <t xml:space="preserve">37cabc89811a4aac</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9b06f77b35e84c8c</t>
+          <t xml:space="preserve">fef91d9ab2784671</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5ad9977a8d1c4253</t>
+          <t xml:space="preserve">3be0fb2a8a7749df</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">31f92a1ead034b48</t>
+          <t xml:space="preserve">6ce84db46c184261</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2496,12 +2496,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">468cddc045ca4b7b</t>
+          <t xml:space="preserve">8e7caa4ed66e4efb</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2569,12 +2569,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013ee57eb8341d1</t>
+          <t xml:space="preserve">141f123893a54359</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2642,12 +2642,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">aa8d02b5fbf94a28</t>
+          <t xml:space="preserve">1cbb53ac389e4e4f</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">398d4c618acc45a3</t>
+          <t xml:space="preserve">f2a754b15f6d4c8f</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">64704f9d5a69420c</t>
+          <t xml:space="preserve">a2797a7baa2648a7</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">13887741cbb94539</t>
+          <t xml:space="preserve">79f20f229d05448f</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -2934,12 +2934,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7d4b7c5df5c44cce</t>
+          <t xml:space="preserve">e4cc3a92a126418b</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f8d0d99be4b8401e</t>
+          <t xml:space="preserve">98d1dff39d3e46e4</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e52b8bef86ac438d</t>
+          <t xml:space="preserve">0a468ed938354984</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fa775a6da1cb4d5e</t>
+          <t xml:space="preserve">70bfce7d367c4f95</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3226,12 +3226,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed5a6db1cac74283</t>
+          <t xml:space="preserve">82a1d86625694f59</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1fa26a74e6ae4013</t>
+          <t xml:space="preserve">6aa386efe193482a</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3372,12 +3372,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">84a90dd3232f4390</t>
+          <t xml:space="preserve">58483e0d63534d81</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cf84ab1483924271</t>
+          <t xml:space="preserve">ccac15acce544976</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9aa1e1bc185c45c2</t>
+          <t xml:space="preserve">eeea878fec1a4e39</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b19d231f9f1642cb</t>
+          <t xml:space="preserve">3281808cd8a24310</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3664,12 +3664,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">88335f97c86d4683</t>
+          <t xml:space="preserve">ee084f881b4c4277</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3737,12 +3737,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e67f39c857a84119</t>
+          <t xml:space="preserve">bfd2d487495a475d</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3810,12 +3810,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b0d1f2069a6c4dfe</t>
+          <t xml:space="preserve">4002405c938340ce</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">48f0e0769eda497f</t>
+          <t xml:space="preserve">2c3718d831d84cfb</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a2222713c09b48c3</t>
+          <t xml:space="preserve">8d3bd6529e364000</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c43c37b4d30844f4</t>
+          <t xml:space="preserve">9f403c4e05ba491d</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6bb1277cf1c4ca1</t>
+          <t xml:space="preserve">e51c186322b749a9</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f99cd09a8dc84282</t>
+          <t xml:space="preserve">1d57c4320a8e40f6</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4248,12 +4248,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3f802c8990a24ffd</t>
+          <t xml:space="preserve">5468092833114e25</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -4321,12 +4321,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a3c5740886f4bd7</t>
+          <t xml:space="preserve">52209dd85e8749cb</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">aa1bcbf434b84fc5</t>
+          <t xml:space="preserve">e46ee3c6e58143da</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4467,12 +4467,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7c90bd7d78d5435b</t>
+          <t xml:space="preserve">1b8c46d94d66492d</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4540,12 +4540,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">474ee4baaa75484b</t>
+          <t xml:space="preserve">73b8402778cf40cd</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4613,12 +4613,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a71043587f1c4f9e</t>
+          <t xml:space="preserve">a87cdbcd2e054eef</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -4686,12 +4686,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">352702a330a74c1a</t>
+          <t xml:space="preserve">063fed2e84374d38</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">efeea583f0a94c4f</t>
+          <t xml:space="preserve">972cf014db7b48e1</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d546bce252de475f</t>
+          <t xml:space="preserve">75e7a0189b214424</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a2ac05137d984d0c</t>
+          <t xml:space="preserve">f71d413a14be4cd0</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7bad23c8c5a04e2a</t>
+          <t xml:space="preserve">e6c7978692824ec0</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3ab97edc34434aa2</t>
+          <t xml:space="preserve">a03874fcecca4ef9</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -5124,12 +5124,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d6a5c9bab05448d2</t>
+          <t xml:space="preserve">babbafe3e04a4ee3</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -5197,12 +5197,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4cf11a7529394543</t>
+          <t xml:space="preserve">9b06f14974c84b53</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c2c7d089d6144a26</t>
+          <t xml:space="preserve">27dc06a7906c492b</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -5343,12 +5343,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0d33e29c2c8a48af</t>
+          <t xml:space="preserve">7faa627f228a430b</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -5416,12 +5416,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">db7a787568f84041</t>
+          <t xml:space="preserve">fe6733dd9b9d4289</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a8bd69893c64df0</t>
+          <t xml:space="preserve">e3b86f7774994e13</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5562,12 +5562,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d7dc9c8d8d324150</t>
+          <t xml:space="preserve">4b61768558bb43a8</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1a5bc56976934b6c</t>
+          <t xml:space="preserve">4d9fc565314c44d5</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">df186b021a9b4ac4</t>
+          <t xml:space="preserve">f3b1c32a58334512</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -5781,12 +5781,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">958e18ca28414f20</t>
+          <t xml:space="preserve">beb6c40a3f3c4e20</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -5854,12 +5854,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">738b756e78144dd5</t>
+          <t xml:space="preserve">1003c552ee04418f</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5d927bfed7be489c</t>
+          <t xml:space="preserve">fbec9f9de31d41e3</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8b819ad1a7b243aa</t>
+          <t xml:space="preserve">7be551491d4a473c</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -6073,12 +6073,12 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">207c8036e9544a5b</t>
+          <t xml:space="preserve">752a8af1113b4233</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b34876514674ae4</t>
+          <t xml:space="preserve">73ebfd80fd204c58</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">02ae9cc353de4931</t>
+          <t xml:space="preserve">8defed31c50d450b</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c3903e3dd1194096</t>
+          <t xml:space="preserve">c34e4ffd686a4157</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">669fae3b7090498c</t>
+          <t xml:space="preserve">da04033bb8534b40</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fc37b09813b741ae</t>
+          <t xml:space="preserve">aff87d85b3514ef7</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fa1c0899e1fa4ca4</t>
+          <t xml:space="preserve">3e489ab7b25e4673</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -6584,12 +6584,12 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145a9b4046b4a00</t>
+          <t xml:space="preserve">067420af5b8140e1</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -6657,12 +6657,12 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">02de51f37798482f</t>
+          <t xml:space="preserve">5c5e592753d34f08</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -6730,12 +6730,12 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">05902968d52e4e17</t>
+          <t xml:space="preserve">04d22da50ee7417d</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2fa27fb139d74b79</t>
+          <t xml:space="preserve">d7f617db7842457c</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -6876,12 +6876,12 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">de0bac88a0094c1c</t>
+          <t xml:space="preserve">b66ef805348e47f9</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -6949,12 +6949,12 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f807361d880944b3</t>
+          <t xml:space="preserve">b318d596a5454dd3</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -7022,12 +7022,12 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a59cb9eb9314901</t>
+          <t xml:space="preserve">74486866e7bc4fc4</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7095,12 +7095,12 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fc9bf6ff345040c3</t>
+          <t xml:space="preserve">1050b6a299b8429e</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -7168,12 +7168,12 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2c72753bddc240af</t>
+          <t xml:space="preserve">cff3758ae9c14f20</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -7241,12 +7241,12 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c3f19a0c80ba4635</t>
+          <t xml:space="preserve">a9d2da3a92584e7a</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -7314,12 +7314,12 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d930236ad0db43cf</t>
+          <t xml:space="preserve">11f73fa62b7944a2</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -7387,12 +7387,12 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">544bf40c9c8444dd</t>
+          <t xml:space="preserve">dc50ae4303434a12</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">65f8290b956d41d5</t>
+          <t xml:space="preserve">b1fdd22410eb4e65</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -7533,12 +7533,12 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad86d264d59447b8</t>
+          <t xml:space="preserve">386ce4ba33b54a50</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">320b948f64764c18</t>
+          <t xml:space="preserve">305104aa12a64962</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -7679,12 +7679,12 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e6ba9f1427d5423b</t>
+          <t xml:space="preserve">9fa1f22a56ff48ec</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -7752,12 +7752,12 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7948e2b8d836497a</t>
+          <t xml:space="preserve">5c4a0113b70640de</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a9819effe71438b</t>
+          <t xml:space="preserve">85e993d1125642c1</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
